--- a/reports/executive/SENTINEL_EXECUTIVE_REPORT.xlsx
+++ b/reports/executive/SENTINEL_EXECUTIVE_REPORT.xlsx
@@ -450,12 +450,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0.9.5.161</t>
+          <t>0.9.5.162</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>v0.9.5.161_report_architecture</t>
+          <t>v0.9.5.162_history_integrity_report_hygiene</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1085,7 +1085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1141,6 +1141,30 @@
         <v>0.8313</v>
       </c>
       <c r="F2" t="n">
+        <v>0.6393</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0.9.5.162-20260723T214043Z-7e18864a</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0.9.5.162</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.8313</v>
+      </c>
+      <c r="F3" t="n">
         <v>0.6393</v>
       </c>
     </row>
@@ -1287,7 +1311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1318,40 +1342,55 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>direct_strategy_matches</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>compatible_strategy_chains</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>true_strategy_conflicts</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>average_expected_resolution_gain</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>average_expected_information_gain</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>average_expected_risk</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>average_expected_utility</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>automatic_fix_executed</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>gold_clearance_created</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>ground_truth_used_as_evidence</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>operational_truth_modified</t>
         </is>
@@ -1360,7 +1399,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>v0.9.5.161_resolution_simulator</t>
+          <t>v0.9.5.162_resolution_simulator</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1373,30 +1412,39 @@
         <v>14</v>
       </c>
       <c r="E2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F2" t="n">
         <v>13</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
+        <v>14</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>0.5792</v>
       </c>
-      <c r="G2" t="n">
+      <c r="J2" t="n">
         <v>0.4955</v>
       </c>
-      <c r="H2" t="n">
+      <c r="K2" t="n">
         <v>0.1525</v>
       </c>
-      <c r="I2" t="n">
+      <c r="L2" t="n">
         <v>0.5114</v>
       </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M2" t="b">
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" t="b">
         <v>0</v>
       </c>
     </row>
